--- a/src/cubes/data/energy_systems/solar-pv.xlsx
+++ b/src/cubes/data/energy_systems/solar-pv.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottjeen/phd/research/CUBES/src/cubes/data/energy_systems/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC13EEE4-9ABA-0145-A984-505BAFE8CA33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{263DF41A-7CCF-CE42-8414-C57F7FB86F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2800" yWindow="3680" windowWidth="28040" windowHeight="17440" xr2:uid="{6613BF47-8E0B-1F4E-9D7F-2739A296C47F}"/>
   </bookViews>
@@ -59,9 +59,6 @@
     <t>https://reader.elsevier.com/reader/sd/pii/S1364032119305179?token=F43FC9B9CCE24F50C8380CBDB1D1C2406682DC94EBCE6517C62E5B8F22FD1FD36C43E011433615F1258A5C1FC14B126F&amp;originRegion=eu-west-1&amp;originCreation=20230501085229</t>
   </si>
   <si>
-    <t>SOLAR PV INSTALLATIONS</t>
-  </si>
-  <si>
     <t>AT</t>
   </si>
   <si>
@@ -159,6 +156,9 @@
   </si>
   <si>
     <t>SOLAR PV PROBABILITY TECHNICAL POTENTIAL UPPER</t>
+  </si>
+  <si>
+    <t>COUNTRY SOLAR PV INSTALLATIONS</t>
   </si>
 </sst>
 </file>
@@ -557,30 +557,30 @@
         <v>0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="E6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="3">
         <v>0.49</v>
@@ -603,7 +603,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" s="3">
         <v>0.49</v>
@@ -626,7 +626,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" s="3">
         <v>0.49</v>
@@ -649,7 +649,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C10" s="3">
         <v>0.49</v>
@@ -672,7 +672,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C11" s="3">
         <v>0.49</v>
@@ -695,7 +695,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" s="3">
         <v>0.49</v>
@@ -718,7 +718,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C13" s="3">
         <v>0.49</v>
@@ -741,7 +741,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" s="3">
         <v>0.49</v>
@@ -764,7 +764,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C15" s="3">
         <v>0.49</v>
@@ -787,7 +787,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C16" s="3">
         <v>0.49</v>
@@ -810,7 +810,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C17" s="3">
         <v>0.49</v>
@@ -833,7 +833,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C18" s="3">
         <v>0.49</v>
@@ -856,7 +856,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C19" s="3">
         <v>0.49</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C20" s="3">
         <v>0.49</v>
@@ -902,7 +902,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C21" s="3">
         <v>0.49</v>
@@ -925,7 +925,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C22" s="3">
         <v>0.49</v>
@@ -948,7 +948,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C23" s="3">
         <v>0.49</v>
@@ -971,7 +971,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C24" s="3">
         <v>0.49</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C25" s="3">
         <v>0.49</v>
@@ -1017,7 +1017,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C26" s="3">
         <v>0.49</v>
@@ -1040,7 +1040,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C27" s="3">
         <v>0.49</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C28" s="3">
         <v>0.49</v>
@@ -1086,7 +1086,7 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C29" s="3">
         <v>0.49</v>
@@ -1109,7 +1109,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C30" s="3">
         <v>0.49</v>
@@ -1132,7 +1132,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C31" s="3">
         <v>0.49</v>
@@ -1155,7 +1155,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C32" s="3">
         <v>0.49</v>
@@ -1178,7 +1178,7 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C33" s="3">
         <v>0.49</v>

--- a/src/cubes/data/energy_systems/solar-pv.xlsx
+++ b/src/cubes/data/energy_systems/solar-pv.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottjeen/phd/research/CUBES/src/cubes/data/energy_systems/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{263DF41A-7CCF-CE42-8414-C57F7FB86F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF467A94-2C2B-E945-B366-79EB2AA93F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2800" yWindow="3680" windowWidth="28040" windowHeight="17440" xr2:uid="{6613BF47-8E0B-1F4E-9D7F-2739A296C47F}"/>
+    <workbookView xWindow="3080" yWindow="4040" windowWidth="28040" windowHeight="17440" xr2:uid="{6613BF47-8E0B-1F4E-9D7F-2739A296C47F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
   <si>
     <t>COUNTRY CODE</t>
   </si>
@@ -140,31 +140,25 @@
     <t>SK</t>
   </si>
   <si>
-    <t>SOLAR PV PANEL EFFICIENCY LOWER</t>
-  </si>
-  <si>
-    <t>SOLAR PV PANEL EFFICIENCY UPPER</t>
-  </si>
-  <si>
-    <t>SOLAR PV ACTIVE AREA FRACTION LOWER</t>
-  </si>
-  <si>
-    <t>SOLAR PV ACTIVE AREA FRACTION UPPER</t>
-  </si>
-  <si>
-    <t>SOLAR PV PROBABILITY TECHNICAL POTENTIAL LOWER</t>
-  </si>
-  <si>
-    <t>SOLAR PV PROBABILITY TECHNICAL POTENTIAL UPPER</t>
-  </si>
-  <si>
     <t>COUNTRY SOLAR PV INSTALLATIONS</t>
+  </si>
+  <si>
+    <t>MEAN SOLAR PV ACTIVE AREA FRACTION</t>
+  </si>
+  <si>
+    <t>SOLAR PV TECHNICAL POTENTIAL INSTALLATIONS</t>
+  </si>
+  <si>
+    <t>MEAN SOLAR PV PANEL EFFICIENCY</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
@@ -202,11 +196,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -521,22 +516,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61CA3E43-411D-7447-8ED5-4DE36A80E3A5}">
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="18.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="60.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="60.1640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.1640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -544,7 +540,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -552,677 +548,416 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="3">
-        <v>0.49</v>
-      </c>
-      <c r="D7" s="3">
-        <v>0.64</v>
+      <c r="C7" s="4">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="D7" s="4">
+        <v>0.17499999999999999</v>
       </c>
       <c r="E7" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="F7" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="G7" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="H7" s="3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="3">
-        <v>0.49</v>
-      </c>
-      <c r="D8" s="3">
-        <v>0.64</v>
+      <c r="C8" s="4">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="D8" s="4">
+        <v>0.17499999999999999</v>
       </c>
       <c r="E8" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="3">
-        <v>0.49</v>
-      </c>
-      <c r="D9" s="3">
-        <v>0.64</v>
+      <c r="C9" s="4">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="D9" s="4">
+        <v>0.17499999999999999</v>
       </c>
       <c r="E9" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="F9" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="G9" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="H9" s="3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="3">
-        <v>0.49</v>
-      </c>
-      <c r="D10" s="3">
-        <v>0.64</v>
+      <c r="C10" s="4">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="D10" s="4">
+        <v>0.17499999999999999</v>
       </c>
       <c r="E10" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="F10" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="G10" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="H10" s="3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="3">
-        <v>0.49</v>
-      </c>
-      <c r="D11" s="3">
-        <v>0.64</v>
+      <c r="C11" s="4">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="D11" s="4">
+        <v>0.17499999999999999</v>
       </c>
       <c r="E11" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="F11" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="G11" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="H11" s="3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="3">
-        <v>0.49</v>
-      </c>
-      <c r="D12" s="3">
-        <v>0.64</v>
+      <c r="C12" s="4">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0.17499999999999999</v>
       </c>
       <c r="E12" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="F12" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="G12" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="H12" s="3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="3">
-        <v>0.49</v>
-      </c>
-      <c r="D13" s="3">
-        <v>0.64</v>
+      <c r="C13" s="4">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="D13" s="4">
+        <v>0.17499999999999999</v>
       </c>
       <c r="E13" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="F13" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="G13" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="H13" s="3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="3">
-        <v>0.49</v>
-      </c>
-      <c r="D14" s="3">
-        <v>0.64</v>
+      <c r="C14" s="4">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="D14" s="4">
+        <v>0.17499999999999999</v>
       </c>
       <c r="E14" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="3">
-        <v>0.49</v>
-      </c>
-      <c r="D15" s="3">
-        <v>0.64</v>
+      <c r="C15" s="4">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="D15" s="4">
+        <v>0.17499999999999999</v>
       </c>
       <c r="E15" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="G15" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="H15" s="3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="3">
-        <v>0.49</v>
-      </c>
-      <c r="D16" s="3">
-        <v>0.64</v>
+      <c r="C16" s="4">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="D16" s="4">
+        <v>0.17499999999999999</v>
       </c>
       <c r="E16" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="F16" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="G16" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="H16" s="3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="3">
-        <v>0.49</v>
-      </c>
-      <c r="D17" s="3">
-        <v>0.64</v>
+      <c r="C17" s="4">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="D17" s="4">
+        <v>0.17499999999999999</v>
       </c>
       <c r="E17" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="F17" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="G17" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="H17" s="3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="3">
-        <v>0.49</v>
-      </c>
-      <c r="D18" s="3">
-        <v>0.64</v>
+      <c r="C18" s="4">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="D18" s="4">
+        <v>0.17499999999999999</v>
       </c>
       <c r="E18" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="F18" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="G18" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="H18" s="3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="3">
-        <v>0.49</v>
-      </c>
-      <c r="D19" s="3">
-        <v>0.64</v>
+      <c r="C19" s="4">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="D19" s="4">
+        <v>0.17499999999999999</v>
       </c>
       <c r="E19" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="F19" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="G19" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="H19" s="3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="C20" s="3">
-        <v>0.49</v>
-      </c>
-      <c r="D20" s="3">
-        <v>0.64</v>
+      <c r="C20" s="4">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="D20" s="4">
+        <v>0.17499999999999999</v>
       </c>
       <c r="E20" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>21</v>
       </c>
-      <c r="C21" s="3">
-        <v>0.49</v>
-      </c>
-      <c r="D21" s="3">
-        <v>0.64</v>
+      <c r="C21" s="4">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0.17499999999999999</v>
       </c>
       <c r="E21" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="F21" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="G21" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="H21" s="3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>22</v>
       </c>
-      <c r="C22" s="3">
-        <v>0.49</v>
-      </c>
-      <c r="D22" s="3">
-        <v>0.64</v>
+      <c r="C22" s="4">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="D22" s="4">
+        <v>0.17499999999999999</v>
       </c>
       <c r="E22" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="3">
-        <v>0.49</v>
-      </c>
-      <c r="D23" s="3">
-        <v>0.64</v>
+      <c r="C23" s="4">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="D23" s="4">
+        <v>0.17499999999999999</v>
       </c>
       <c r="E23" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="F23" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="G23" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="H23" s="3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="3">
-        <v>0.49</v>
-      </c>
-      <c r="D24" s="3">
-        <v>0.64</v>
+      <c r="C24" s="4">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="D24" s="4">
+        <v>0.17499999999999999</v>
       </c>
       <c r="E24" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>25</v>
       </c>
-      <c r="C25" s="3">
-        <v>0.49</v>
-      </c>
-      <c r="D25" s="3">
-        <v>0.64</v>
+      <c r="C25" s="4">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="D25" s="4">
+        <v>0.17499999999999999</v>
       </c>
       <c r="E25" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="F25" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="G25" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="H25" s="3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="3">
-        <v>0.49</v>
-      </c>
-      <c r="D26" s="3">
-        <v>0.64</v>
+      <c r="C26" s="4">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="D26" s="4">
+        <v>0.17499999999999999</v>
       </c>
       <c r="E26" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="F26" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="G26" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="H26" s="3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="3">
-        <v>0.49</v>
-      </c>
-      <c r="D27" s="3">
-        <v>0.64</v>
+      <c r="C27" s="4">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="D27" s="4">
+        <v>0.17499999999999999</v>
       </c>
       <c r="E27" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="F27" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="G27" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="H27" s="3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="3">
-        <v>0.49</v>
-      </c>
-      <c r="D28" s="3">
-        <v>0.64</v>
+      <c r="C28" s="4">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="D28" s="4">
+        <v>0.17499999999999999</v>
       </c>
       <c r="E28" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="F28" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="G28" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="H28" s="3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="3">
-        <v>0.49</v>
-      </c>
-      <c r="D29" s="3">
-        <v>0.64</v>
+      <c r="C29" s="4">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="D29" s="4">
+        <v>0.17499999999999999</v>
       </c>
       <c r="E29" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>30</v>
       </c>
-      <c r="C30" s="3">
-        <v>0.49</v>
-      </c>
-      <c r="D30" s="3">
-        <v>0.64</v>
+      <c r="C30" s="4">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="D30" s="4">
+        <v>0.17499999999999999</v>
       </c>
       <c r="E30" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="F30" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="G30" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="H30" s="3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>31</v>
       </c>
-      <c r="C31" s="3">
-        <v>0.49</v>
-      </c>
-      <c r="D31" s="3">
-        <v>0.64</v>
+      <c r="C31" s="4">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="D31" s="4">
+        <v>0.17499999999999999</v>
       </c>
       <c r="E31" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="F31" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="G31" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="H31" s="3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>32</v>
       </c>
-      <c r="C32" s="3">
-        <v>0.49</v>
-      </c>
-      <c r="D32" s="3">
-        <v>0.64</v>
+      <c r="C32" s="4">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="D32" s="4">
+        <v>0.17499999999999999</v>
       </c>
       <c r="E32" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>33</v>
       </c>
-      <c r="C33" s="3">
-        <v>0.49</v>
-      </c>
-      <c r="D33" s="3">
-        <v>0.64</v>
+      <c r="C33" s="4">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="D33" s="4">
+        <v>0.17499999999999999</v>
       </c>
       <c r="E33" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="F33" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="G33" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="H33" s="3">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>1</v>
       </c>
       <c r="B34" s="1">
         <v>1067642</v>
       </c>
-      <c r="C34" s="3">
-        <v>0.49</v>
-      </c>
-      <c r="D34" s="3">
-        <v>0.64</v>
+      <c r="C34" s="4">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="D34" s="4">
+        <v>0.17499999999999999</v>
       </c>
       <c r="E34" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="F34" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="G34" s="3">
-        <v>0.7</v>
-      </c>
-      <c r="H34" s="3">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>

--- a/src/cubes/data/energy_systems/solar-pv.xlsx
+++ b/src/cubes/data/energy_systems/solar-pv.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10409"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10514"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottjeen/phd/research/CUBES/src/cubes/data/energy_systems/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF467A94-2C2B-E945-B366-79EB2AA93F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7FDAF6E-EE1E-BD49-8D54-42DACEA057A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3080" yWindow="4040" windowWidth="28040" windowHeight="17440" xr2:uid="{6613BF47-8E0B-1F4E-9D7F-2739A296C47F}"/>
   </bookViews>
@@ -143,13 +143,13 @@
     <t>COUNTRY SOLAR PV INSTALLATIONS</t>
   </si>
   <si>
-    <t>MEAN SOLAR PV ACTIVE AREA FRACTION</t>
-  </si>
-  <si>
     <t>SOLAR PV TECHNICAL POTENTIAL INSTALLATIONS</t>
   </si>
   <si>
     <t>MEAN SOLAR PV PANEL EFFICIENCY</t>
+  </si>
+  <si>
+    <t>SOLAR PV ACTIVE AREA FRACTION</t>
   </si>
 </sst>
 </file>
@@ -556,13 +556,13 @@
         <v>34</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -576,7 +576,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="E7" s="3">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
@@ -590,7 +590,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="E8" s="3">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -604,7 +604,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="E9" s="3">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -618,7 +618,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="E10" s="3">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
@@ -632,7 +632,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="E11" s="3">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
@@ -646,7 +646,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="E12" s="3">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
@@ -660,7 +660,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="E13" s="3">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
@@ -674,7 +674,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="E14" s="3">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
@@ -688,7 +688,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="E15" s="3">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
@@ -702,7 +702,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="E16" s="3">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
@@ -716,7 +716,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="E17" s="3">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
@@ -730,7 +730,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="E18" s="3">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
@@ -744,7 +744,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="E19" s="3">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
@@ -758,7 +758,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="E20" s="3">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
@@ -772,7 +772,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="E21" s="3">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
@@ -786,7 +786,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="E22" s="3">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
@@ -800,7 +800,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="E23" s="3">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
@@ -814,7 +814,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="E24" s="3">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
@@ -828,7 +828,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="E25" s="3">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
@@ -842,7 +842,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="E26" s="3">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
@@ -856,7 +856,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="E27" s="3">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
@@ -870,7 +870,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="E28" s="3">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
@@ -884,7 +884,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="E29" s="3">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
@@ -898,7 +898,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="E30" s="3">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
@@ -912,7 +912,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="E31" s="3">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
@@ -926,7 +926,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="E32" s="3">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
@@ -940,7 +940,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="E33" s="3">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
@@ -957,7 +957,7 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="E34" s="3">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
     </row>
   </sheetData>
